--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-19T20:30:21Z</t>
+          <t>2026-10-20T18:08:31Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20T18:08:31Z</t>
+          <t>2026-10-21T12:53:13Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-21T12:53:13Z</t>
+          <t>2026-10-22T09:28:33Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-22T09:28:33Z</t>
+          <t>2026-10-23T09:24:48Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-23T09:24:48Z</t>
+          <t>2026-10-24T08:56:14Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-24T08:56:14Z</t>
+          <t>2026-10-25T09:13:05Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-25T09:13:05Z</t>
+          <t>2026-10-26T10:15:06Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-26T10:15:06Z</t>
+          <t>2026-10-27T09:52:25Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-27T09:52:25Z</t>
+          <t>2026-10-28T10:39:31Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-28T10:39:31Z</t>
+          <t>2026-10-29T10:57:12Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29T10:57:12Z</t>
+          <t>2026-10-30T10:55:00Z</t>
         </is>
       </c>
     </row>

--- a/data/excel/sube_mensual.xlsx
+++ b/data/excel/sube_mensual.xlsx
@@ -6679,7 +6679,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-30T10:55:00Z</t>
+          <t>2026-10-31T10:27:05Z</t>
         </is>
       </c>
     </row>
